--- a/data/trans_camb/BARTHEL_R2-Provincia-trans_camb.xlsx
+++ b/data/trans_camb/BARTHEL_R2-Provincia-trans_camb.xlsx
@@ -624,47 +624,47 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
-          <t>-5,5</t>
+          <t>5,5</t>
         </is>
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>-15,59</t>
+          <t>15,59</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>4,1</t>
+          <t>-4,1</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>-39,4</t>
+          <t>39,4</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t>-30,34</t>
+          <t>30,34</t>
         </is>
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>-7,05</t>
+          <t>7,05</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>-23,29</t>
+          <t>23,29</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
         <is>
-          <t>-23,71</t>
+          <t>23,71</t>
         </is>
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>-1,81</t>
+          <t>1,81</t>
         </is>
       </c>
     </row>
@@ -677,47 +677,47 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-19,98; 8,35</t>
+          <t>-8,77; 20,57</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-32,13; -0,19</t>
+          <t>-0,31; 32,05</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-4,67; 16,27</t>
+          <t>-16,44; 5,62</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-55,59; -21,95</t>
+          <t>22,45; 54,52</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-47,1; -14,34</t>
+          <t>14,39; 47,99</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>-16,42; 6,44</t>
+          <t>-5,98; 16,11</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>-35,05; -11,65</t>
+          <t>11,3; 34,19</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>-35,42; -11,85</t>
+          <t>12,77; 37,33</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>-8,94; 7,21</t>
+          <t>-6,7; 9,08</t>
         </is>
       </c>
     </row>
@@ -730,47 +730,47 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>-6,1%</t>
+          <t>55,25%</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>-17,31%</t>
+          <t>156,69%</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>4,55%</t>
+          <t>-41,18%</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>-41,96%</t>
+          <t>643,99%</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>-32,32%</t>
+          <t>495,98%</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>-7,51%</t>
+          <t>115,31%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>-25,3%</t>
+          <t>293,54%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>-25,76%</t>
+          <t>298,87%</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>-1,96%</t>
+          <t>22,78%</t>
         </is>
       </c>
     </row>
@@ -783,47 +783,47 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-21,72; 9,01</t>
+          <t>-63,81; 597,84</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-34,97; -0,68</t>
+          <t>-16,31; 738,07</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-4,83; 20,66</t>
+          <t>-88,83; 289,62</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>-57,94; -25,28</t>
+          <t>98,75; —</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>-49,1; -16,19</t>
+          <t>31,31; —</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>-16,84; 7,11</t>
+          <t>-50,96; —</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>-37,36; -13,18</t>
+          <t>70,19; 1067,22</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>-38,12; -13,98</t>
+          <t>88,62; 995,87</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>-9,28; 8,27</t>
+          <t>-51,93; 299,96</t>
         </is>
       </c>
     </row>
@@ -840,47 +840,47 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>-11,79</t>
+          <t>11,79</t>
         </is>
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>-1,78</t>
+          <t>1,78</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>-7,39</t>
+          <t>7,39</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>-20,36</t>
+          <t>20,36</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
         <is>
-          <t>-8,24</t>
+          <t>8,24</t>
         </is>
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>-13,62</t>
+          <t>13,62</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>-16,32</t>
+          <t>16,32</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>-5,21</t>
+          <t>5,21</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>-11,39</t>
+          <t>11,39</t>
         </is>
       </c>
     </row>
@@ -893,47 +893,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-24,59; -2,4</t>
+          <t>1,87; 23,53</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-8,6; 5,39</t>
+          <t>-5,75; 8,5</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-15,18; 1,55</t>
+          <t>-0,42; 15,33</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-32,44; -8,43</t>
+          <t>8,69; 32,01</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-19,21; 2,47</t>
+          <t>-2,55; 20,39</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-22,06; -3,33</t>
+          <t>4,38; 22,19</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>-25,27; -8,34</t>
+          <t>7,94; 24,72</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>-13,3; 2,54</t>
+          <t>-2,13; 12,89</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>-17,33; -4,5</t>
+          <t>4,92; 18,01</t>
         </is>
       </c>
     </row>
@@ -946,47 +946,47 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
-          <t>-12,35%</t>
+          <t>261,99%</t>
         </is>
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>-1,87%</t>
+          <t>39,62%</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>-7,74%</t>
+          <t>164,22%</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>-23,64%</t>
+          <t>146,73%</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
         <is>
-          <t>-9,57%</t>
+          <t>59,39%</t>
         </is>
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>-15,81%</t>
+          <t>98,14%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>-18,15%</t>
+          <t>161,92%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
         <is>
-          <t>-5,8%</t>
+          <t>51,74%</t>
         </is>
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>-12,67%</t>
+          <t>113,05%</t>
         </is>
       </c>
     </row>
@@ -999,47 +999,47 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-25,32; -2,53</t>
+          <t>-29,43; 1652,66</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-8,83; 6,06</t>
+          <t>-77,47; 653,82</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-15,57; 1,15</t>
+          <t>-28,87; 1239,95</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-36,56; -10,79</t>
+          <t>44,28; 351,58</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-21,56; 3,01</t>
+          <t>-18,16; 229,58</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>-24,28; -4,2</t>
+          <t>17,75; 262,06</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>-27,39; -9,78</t>
+          <t>53,04; 384,9</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>-14,23; 2,73</t>
+          <t>-19,02; 199,5</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>-18,93; -5,44</t>
+          <t>33,16; 272,66</t>
         </is>
       </c>
     </row>
@@ -1056,47 +1056,47 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>-10,87</t>
+          <t>10,87</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>-2,36</t>
+          <t>2,36</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>-19,24</t>
+          <t>19,24</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>-9,47</t>
+          <t>9,47</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>3,05</t>
+          <t>-3,05</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>-13,02</t>
+          <t>13,02</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>-9,8</t>
+          <t>9,8</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>1,14</t>
+          <t>-1,14</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>-15,27</t>
+          <t>15,27</t>
         </is>
       </c>
     </row>
@@ -1109,47 +1109,47 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-23,75; 1,77</t>
+          <t>-0,38; 24,87</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-10,48; 7,0</t>
+          <t>-7,25; 10,93</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-28,25; -6,94</t>
+          <t>8,48; 29,64</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-22,02; 2,93</t>
+          <t>-3,3; 22,45</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-8,06; 13,92</t>
+          <t>-13,72; 8,17</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>-22,17; -1,66</t>
+          <t>2,57; 23,31</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>-19,08; -1,16</t>
+          <t>1,24; 18,79</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>-6,37; 8,71</t>
+          <t>-8,4; 6,54</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>-22,01; -7,24</t>
+          <t>7,89; 22,5</t>
         </is>
       </c>
     </row>
@@ -1162,47 +1162,47 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
-          <t>-11,53%</t>
+          <t>188,67%</t>
         </is>
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>-2,5%</t>
+          <t>40,92%</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>-20,42%</t>
+          <t>334,18%</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>-10,91%</t>
+          <t>71,27%</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
         <is>
-          <t>3,51%</t>
+          <t>-22,94%</t>
         </is>
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>-15,02%</t>
+          <t>98,04%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>-10,94%</t>
+          <t>93,95%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
         <is>
-          <t>1,27%</t>
+          <t>-10,89%</t>
         </is>
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>-17,05%</t>
+          <t>146,38%</t>
         </is>
       </c>
     </row>
@@ -1215,47 +1215,47 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>-24,83; 1,6</t>
+          <t>-33,13; 1489,81</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>-10,94; 7,92</t>
+          <t>-77,73; —</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>-29,13; -8,37</t>
+          <t>42,42; 1485,87</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>-25,0; 3,46</t>
+          <t>-19,0; 275,37</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>-8,85; 17,35</t>
+          <t>-77,0; 123,93</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>-24,33; -2,2</t>
+          <t>11,73; 318,6</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>-20,61; -1,29</t>
+          <t>6,52; 297,94</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>-6,77; 10,24</t>
+          <t>-61,87; 96,33</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>-23,91; -8,38</t>
+          <t>48,07; 375,55</t>
         </is>
       </c>
     </row>
@@ -1272,47 +1272,47 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
-          <t>-8,96</t>
+          <t>8,96</t>
         </is>
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>-12,26</t>
+          <t>12,26</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>-4,68</t>
+          <t>4,68</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>-8,01</t>
+          <t>8,01</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
         <is>
-          <t>-6,57</t>
+          <t>6,57</t>
         </is>
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>-4,47</t>
+          <t>4,47</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>-8,39</t>
+          <t>8,39</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
         <is>
-          <t>-9,06</t>
+          <t>9,06</t>
         </is>
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>-4,64</t>
+          <t>4,64</t>
         </is>
       </c>
     </row>
@@ -1325,47 +1325,47 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>-19,84; 0,86</t>
+          <t>-0,28; 19,89</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>-24,64; -2,27</t>
+          <t>3,06; 23,23</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>-12,59; 2,3</t>
+          <t>-3,47; 11,49</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>-20,2; 5,44</t>
+          <t>-4,32; 20,15</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>-20,23; 6,24</t>
+          <t>-5,96; 20,67</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>-13,55; 6,94</t>
+          <t>-5,45; 13,75</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>-17,09; 0,42</t>
+          <t>-0,11; 17,06</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>-17,41; 0,16</t>
+          <t>0,81; 18,43</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>-10,68; 2,1</t>
+          <t>-2,12; 10,55</t>
         </is>
       </c>
     </row>
@@ -1378,47 +1378,47 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>-9,4%</t>
+          <t>191,35%</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>-12,87%</t>
+          <t>262,02%</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>-4,91%</t>
+          <t>100,07%</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>-9,51%</t>
+          <t>51,08%</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>-7,8%</t>
+          <t>41,91%</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>-5,3%</t>
+          <t>28,46%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>-9,43%</t>
+          <t>76,3%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>-10,18%</t>
+          <t>82,36%</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>-5,21%</t>
+          <t>42,13%</t>
         </is>
       </c>
     </row>
@@ -1431,47 +1431,47 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>-20,71; 0,76</t>
+          <t>-28,45; 1216,81</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>-25,31; -2,47</t>
+          <t>4,43; 1328,51</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>-12,82; 2,51</t>
+          <t>-51,0; 632,63</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>-22,8; 6,93</t>
+          <t>-24,1; 220,76</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>-22,65; 7,95</t>
+          <t>-32,25; 204,71</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>-14,88; 9,33</t>
+          <t>-25,82; 152,53</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>-18,58; 0,51</t>
+          <t>-3,96; 241,6</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>-18,93; 0,16</t>
+          <t>3,08; 256,01</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>-11,52; 2,45</t>
+          <t>-13,64; 157,67</t>
         </is>
       </c>
     </row>
@@ -1488,47 +1488,47 @@
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
-          <t>-3,67</t>
+          <t>3,67</t>
         </is>
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>13,71</t>
+          <t>-13,71</t>
         </is>
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>0,05</t>
+          <t>-0,05</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>-8,24</t>
+          <t>8,24</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
         <is>
-          <t>-1,14</t>
+          <t>1,14</t>
         </is>
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>-1,96</t>
+          <t>1,96</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>-6,56</t>
+          <t>6,56</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
         <is>
-          <t>5,74</t>
+          <t>-5,74</t>
         </is>
       </c>
       <c r="K20" s="2" t="inlineStr">
         <is>
-          <t>-1,38</t>
+          <t>1,38</t>
         </is>
       </c>
     </row>
@@ -1541,47 +1541,47 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>-23,12; 14,68</t>
+          <t>-14,99; 24,33</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>0,91; 29,06</t>
+          <t>-28,81; -1,83</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>-13,96; 17,9</t>
+          <t>-16,09; 13,35</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>-27,71; 8,78</t>
+          <t>-9,92; 25,82</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>-19,5; 17,63</t>
+          <t>-15,31; 16,57</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>-16,31; 13,79</t>
+          <t>-13,39; 14,21</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>-19,8; 6,98</t>
+          <t>-7,64; 19,86</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>-6,45; 17,52</t>
+          <t>-17,6; 6,37</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>-12,15; 10,05</t>
+          <t>-9,27; 11,22</t>
         </is>
       </c>
     </row>
@@ -1594,47 +1594,47 @@
       </c>
       <c r="C22" s="2" t="inlineStr">
         <is>
-          <t>-4,45%</t>
+          <t>20,89%</t>
         </is>
       </c>
       <c r="D22" s="2" t="inlineStr">
         <is>
-          <t>16,63%</t>
+          <t>-78,15%</t>
         </is>
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>0,06%</t>
+          <t>-0,3%</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>-10,43%</t>
+          <t>39,16%</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
         <is>
-          <t>-1,44%</t>
+          <t>5,41%</t>
         </is>
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>-2,48%</t>
+          <t>9,32%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>-8,16%</t>
+          <t>33,5%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
         <is>
-          <t>7,14%</t>
+          <t>-29,33%</t>
         </is>
       </c>
       <c r="K22" s="2" t="inlineStr">
         <is>
-          <t>-1,72%</t>
+          <t>7,04%</t>
         </is>
       </c>
     </row>
@@ -1647,47 +1647,47 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>-26,19; 20,32</t>
+          <t>-63,66; 288,05</t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>1,03; 43,23</t>
+          <t>-100,0; 31,72</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>-15,4; 25,34</t>
+          <t>-61,41; 154,78</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>-31,73; 12,29</t>
+          <t>-35,36; 209,11</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>-21,81; 25,99</t>
+          <t>-52,26; 143,68</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>-17,99; 20,5</t>
+          <t>-42,24; 127,07</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>-23,92; 8,99</t>
+          <t>-30,38; 159,39</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
         <is>
-          <t>-7,13; 23,89</t>
+          <t>-65,26; 58,44</t>
         </is>
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>-13,59; 14,22</t>
+          <t>-34,54; 95,08</t>
         </is>
       </c>
     </row>
@@ -1704,47 +1704,47 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>-14,8</t>
+          <t>14,8</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>-12,87</t>
+          <t>12,87</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>-14,77</t>
+          <t>14,77</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>-13,61</t>
+          <t>13,61</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
         <is>
-          <t>-19,2</t>
+          <t>19,2</t>
         </is>
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>-19,15</t>
+          <t>19,15</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>-13,98</t>
+          <t>13,98</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
         <is>
-          <t>-16,45</t>
+          <t>16,45</t>
         </is>
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>-16,59</t>
+          <t>16,59</t>
         </is>
       </c>
     </row>
@@ -1757,47 +1757,47 @@
       </c>
       <c r="C25" s="2" t="inlineStr">
         <is>
-          <t>-30,3; -1,33</t>
+          <t>2,47; 29,12</t>
         </is>
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t>-27,18; -0,51</t>
+          <t>1,68; 27,75</t>
         </is>
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>-23,9; -3,41</t>
+          <t>4,07; 24,09</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>-27,16; 0,95</t>
+          <t>-0,1; 27,32</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
         <is>
-          <t>-35,59; -4,0</t>
+          <t>5,09; 35,56</t>
         </is>
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>-29,36; -7,35</t>
+          <t>6,31; 28,77</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>-24,06; -4,36</t>
+          <t>4,7; 22,52</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
         <is>
-          <t>-26,87; -6,61</t>
+          <t>6,11; 27,17</t>
         </is>
       </c>
       <c r="K25" s="2" t="inlineStr">
         <is>
-          <t>-23,23; -8,0</t>
+          <t>8,51; 24,36</t>
         </is>
       </c>
     </row>
@@ -1810,47 +1810,47 @@
       </c>
       <c r="C26" s="2" t="inlineStr">
         <is>
-          <t>-16,05%</t>
+          <t>189,41%</t>
         </is>
       </c>
       <c r="D26" s="2" t="inlineStr">
         <is>
-          <t>-13,96%</t>
+          <t>164,71%</t>
         </is>
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>-16,02%</t>
+          <t>189,08%</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>-15,75%</t>
+          <t>100,02%</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
         <is>
-          <t>-22,22%</t>
+          <t>141,09%</t>
         </is>
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>-22,16%</t>
+          <t>140,71%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>-15,76%</t>
+          <t>123,96%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
         <is>
-          <t>-18,55%</t>
+          <t>145,88%</t>
         </is>
       </c>
       <c r="K26" s="2" t="inlineStr">
         <is>
-          <t>-18,7%</t>
+          <t>147,1%</t>
         </is>
       </c>
     </row>
@@ -1863,47 +1863,47 @@
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>-32,15; -2,73</t>
+          <t>-9,79; 1188,72</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>-28,89; -0,9</t>
+          <t>-5,22; 1061,11</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>-25,36; -4,33</t>
+          <t>13,33; 1116,85</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>-30,31; 0,72</t>
+          <t>-6,7; 345,25</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
         <is>
-          <t>-39,02; -4,98</t>
+          <t>10,76; 428,83</t>
         </is>
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>-32,27; -9,69</t>
+          <t>29,78; 458,44</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>-26,21; -5,07</t>
+          <t>24,01; 339,46</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
         <is>
-          <t>-30,0; -7,89</t>
+          <t>34,71; 407,14</t>
         </is>
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>-25,13; -9,54</t>
+          <t>43,48; 403,07</t>
         </is>
       </c>
     </row>
@@ -1920,47 +1920,47 @@
       </c>
       <c r="C28" s="2" t="inlineStr">
         <is>
-          <t>-10,58</t>
+          <t>10,58</t>
         </is>
       </c>
       <c r="D28" s="2" t="inlineStr">
         <is>
-          <t>-8,98</t>
+          <t>8,98</t>
         </is>
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>-7,71</t>
+          <t>7,71</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>-17,66</t>
+          <t>17,66</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
         <is>
-          <t>-22,79</t>
+          <t>22,79</t>
         </is>
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>-5,42</t>
+          <t>5,42</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>-14,54</t>
+          <t>14,54</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
         <is>
-          <t>-16,83</t>
+          <t>16,83</t>
         </is>
       </c>
       <c r="K28" s="2" t="inlineStr">
         <is>
-          <t>-6,03</t>
+          <t>6,03</t>
         </is>
       </c>
     </row>
@@ -1973,47 +1973,47 @@
       </c>
       <c r="C29" s="2" t="inlineStr">
         <is>
-          <t>-20,14; -3,05</t>
+          <t>2,99; 19,34</t>
         </is>
       </c>
       <c r="D29" s="2" t="inlineStr">
         <is>
-          <t>-16,42; -2,34</t>
+          <t>1,88; 17,16</t>
         </is>
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>-14,32; -1,61</t>
+          <t>1,49; 13,92</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>-25,88; -10,54</t>
+          <t>9,83; 25,59</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
         <is>
-          <t>-32,76; -15,45</t>
+          <t>14,42; 31,58</t>
         </is>
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>-22,74; 4,36</t>
+          <t>-5,29; 22,69</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>-20,33; -9,22</t>
+          <t>9,23; 20,86</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
         <is>
-          <t>-23,03; -11,27</t>
+          <t>11,72; 23,21</t>
         </is>
       </c>
       <c r="K29" s="2" t="inlineStr">
         <is>
-          <t>-15,41; 3,03</t>
+          <t>-3,49; 15,36</t>
         </is>
       </c>
     </row>
@@ -2026,47 +2026,47 @@
       </c>
       <c r="C30" s="2" t="inlineStr">
         <is>
-          <t>-11,04%</t>
+          <t>256,83%</t>
         </is>
       </c>
       <c r="D30" s="2" t="inlineStr">
         <is>
-          <t>-9,37%</t>
+          <t>217,93%</t>
         </is>
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>-8,04%</t>
+          <t>187,09%</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>-18,42%</t>
+          <t>426,54%</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
         <is>
-          <t>-23,77%</t>
+          <t>550,32%</t>
         </is>
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>-5,65%</t>
+          <t>130,83%</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>-15,16%</t>
+          <t>351,87%</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
         <is>
-          <t>-17,55%</t>
+          <t>407,29%</t>
         </is>
       </c>
       <c r="K30" s="2" t="inlineStr">
         <is>
-          <t>-6,29%</t>
+          <t>146,01%</t>
         </is>
       </c>
     </row>
@@ -2079,47 +2079,47 @@
       </c>
       <c r="C31" s="2" t="inlineStr">
         <is>
-          <t>-20,74; -3,19</t>
+          <t>17,7; 1106,13</t>
         </is>
       </c>
       <c r="D31" s="2" t="inlineStr">
         <is>
-          <t>-17,22; -2,72</t>
+          <t>-0,64; 942,18</t>
         </is>
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>-14,63; -1,89</t>
+          <t>9,68; 763,12</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>-26,59; -11,39</t>
+          <t>117,1; 1449,72</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
         <is>
-          <t>-33,64; -16,34</t>
+          <t>168,74; 2130,65</t>
         </is>
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>-23,53; 4,76</t>
+          <t>-66,02; 786,93</t>
         </is>
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>-21,1; -9,82</t>
+          <t>121,79; 811,2</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr">
         <is>
-          <t>-23,79; -11,83</t>
+          <t>159,5; 937,9</t>
         </is>
       </c>
       <c r="K31" s="2" t="inlineStr">
         <is>
-          <t>-16,08; 3,24</t>
+          <t>-37,51; 467,52</t>
         </is>
       </c>
     </row>
@@ -2136,47 +2136,47 @@
       </c>
       <c r="C32" s="2" t="inlineStr">
         <is>
-          <t>4,1</t>
+          <t>-4,1</t>
         </is>
       </c>
       <c r="D32" s="2" t="inlineStr">
         <is>
-          <t>3,99</t>
+          <t>-3,99</t>
         </is>
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>4,39</t>
+          <t>-4,39</t>
         </is>
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t>-0,43</t>
+          <t>0,43</t>
         </is>
       </c>
       <c r="G32" s="2" t="inlineStr">
         <is>
-          <t>5,7</t>
+          <t>-5,7</t>
         </is>
       </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
-          <t>0,82</t>
+          <t>-0,82</t>
         </is>
       </c>
       <c r="I32" s="2" t="inlineStr">
         <is>
-          <t>1,5</t>
+          <t>-1,5</t>
         </is>
       </c>
       <c r="J32" s="2" t="inlineStr">
         <is>
-          <t>5,02</t>
+          <t>-5,02</t>
         </is>
       </c>
       <c r="K32" s="2" t="inlineStr">
         <is>
-          <t>2,51</t>
+          <t>-2,51</t>
         </is>
       </c>
     </row>
@@ -2189,47 +2189,47 @@
       </c>
       <c r="C33" s="2" t="inlineStr">
         <is>
-          <t>-5,31; 12,66</t>
+          <t>-12,67; 4,2</t>
         </is>
       </c>
       <c r="D33" s="2" t="inlineStr">
         <is>
-          <t>-4,35; 12,14</t>
+          <t>-11,9; 3,74</t>
         </is>
       </c>
       <c r="E33" s="2" t="inlineStr">
         <is>
-          <t>-2,45; 12,04</t>
+          <t>-12,03; 2,64</t>
         </is>
       </c>
       <c r="F33" s="2" t="inlineStr">
         <is>
-          <t>-10,28; 8,92</t>
+          <t>-8,72; 9,42</t>
         </is>
       </c>
       <c r="G33" s="2" t="inlineStr">
         <is>
-          <t>-3,55; 14,26</t>
+          <t>-14,17; 3,74</t>
         </is>
       </c>
       <c r="H33" s="2" t="inlineStr">
         <is>
-          <t>-6,49; 9,92</t>
+          <t>-9,19; 6,79</t>
         </is>
       </c>
       <c r="I33" s="2" t="inlineStr">
         <is>
-          <t>-5,42; 7,89</t>
+          <t>-7,88; 5,52</t>
         </is>
       </c>
       <c r="J33" s="2" t="inlineStr">
         <is>
-          <t>-1,94; 10,45</t>
+          <t>-10,73; 1,28</t>
         </is>
       </c>
       <c r="K33" s="2" t="inlineStr">
         <is>
-          <t>-3,02; 8,15</t>
+          <t>-7,98; 2,95</t>
         </is>
       </c>
     </row>
@@ -2242,47 +2242,47 @@
       </c>
       <c r="C34" s="2" t="inlineStr">
         <is>
-          <t>4,71%</t>
+          <t>-31,26%</t>
         </is>
       </c>
       <c r="D34" s="2" t="inlineStr">
         <is>
-          <t>4,59%</t>
+          <t>-30,46%</t>
         </is>
       </c>
       <c r="E34" s="2" t="inlineStr">
         <is>
-          <t>5,05%</t>
+          <t>-33,48%</t>
         </is>
       </c>
       <c r="F34" s="2" t="inlineStr">
         <is>
-          <t>-0,53%</t>
+          <t>2,25%</t>
         </is>
       </c>
       <c r="G34" s="2" t="inlineStr">
         <is>
-          <t>7,05%</t>
+          <t>-29,84%</t>
         </is>
       </c>
       <c r="H34" s="2" t="inlineStr">
         <is>
-          <t>1,01%</t>
+          <t>-4,29%</t>
         </is>
       </c>
       <c r="I34" s="2" t="inlineStr">
         <is>
-          <t>1,79%</t>
+          <t>-9,02%</t>
         </is>
       </c>
       <c r="J34" s="2" t="inlineStr">
         <is>
-          <t>6,02%</t>
+          <t>-30,31%</t>
         </is>
       </c>
       <c r="K34" s="2" t="inlineStr">
         <is>
-          <t>3,0%</t>
+          <t>-15,13%</t>
         </is>
       </c>
     </row>
@@ -2295,47 +2295,47 @@
       </c>
       <c r="C35" s="2" t="inlineStr">
         <is>
-          <t>-5,74; 15,72</t>
+          <t>-72,28; 57,16</t>
         </is>
       </c>
       <c r="D35" s="2" t="inlineStr">
         <is>
-          <t>-4,74; 14,95</t>
+          <t>-67,22; 49,7</t>
         </is>
       </c>
       <c r="E35" s="2" t="inlineStr">
         <is>
-          <t>-2,63; 15,07</t>
+          <t>-64,66; 36,86</t>
         </is>
       </c>
       <c r="F35" s="2" t="inlineStr">
         <is>
-          <t>-11,91; 11,77</t>
+          <t>-37,98; 69,05</t>
         </is>
       </c>
       <c r="G35" s="2" t="inlineStr">
         <is>
-          <t>-4,1; 19,16</t>
+          <t>-61,61; 27,24</t>
         </is>
       </c>
       <c r="H35" s="2" t="inlineStr">
         <is>
-          <t>-7,6; 13,29</t>
+          <t>-37,08; 51,72</t>
         </is>
       </c>
       <c r="I35" s="2" t="inlineStr">
         <is>
-          <t>-6,24; 9,96</t>
+          <t>-39,3; 44,22</t>
         </is>
       </c>
       <c r="J35" s="2" t="inlineStr">
         <is>
-          <t>-2,11; 13,06</t>
+          <t>-56,61; 7,74</t>
         </is>
       </c>
       <c r="K35" s="2" t="inlineStr">
         <is>
-          <t>-3,46; 10,37</t>
+          <t>-39,12; 23,05</t>
         </is>
       </c>
     </row>
@@ -2352,47 +2352,47 @@
       </c>
       <c r="C36" s="2" t="inlineStr">
         <is>
-          <t>-6,99</t>
+          <t>6,99</t>
         </is>
       </c>
       <c r="D36" s="2" t="inlineStr">
         <is>
-          <t>-3,91</t>
+          <t>3,91</t>
         </is>
       </c>
       <c r="E36" s="2" t="inlineStr">
         <is>
-          <t>-5,19</t>
+          <t>5,19</t>
         </is>
       </c>
       <c r="F36" s="2" t="inlineStr">
         <is>
-          <t>-12,44</t>
+          <t>12,44</t>
         </is>
       </c>
       <c r="G36" s="2" t="inlineStr">
         <is>
-          <t>-8,23</t>
+          <t>8,23</t>
         </is>
       </c>
       <c r="H36" s="2" t="inlineStr">
         <is>
-          <t>-4,84</t>
+          <t>4,84</t>
         </is>
       </c>
       <c r="I36" s="2" t="inlineStr">
         <is>
-          <t>-10,08</t>
+          <t>10,08</t>
         </is>
       </c>
       <c r="J36" s="2" t="inlineStr">
         <is>
-          <t>-6,34</t>
+          <t>6,34</t>
         </is>
       </c>
       <c r="K36" s="2" t="inlineStr">
         <is>
-          <t>-5,19</t>
+          <t>5,19</t>
         </is>
       </c>
     </row>
@@ -2405,47 +2405,47 @@
       </c>
       <c r="C37" s="2" t="inlineStr">
         <is>
-          <t>-10,81; -2,97</t>
+          <t>2,99; 10,37</t>
         </is>
       </c>
       <c r="D37" s="2" t="inlineStr">
         <is>
-          <t>-7,29; -0,33</t>
+          <t>0,31; 7,05</t>
         </is>
       </c>
       <c r="E37" s="2" t="inlineStr">
         <is>
-          <t>-8,36; -2,02</t>
+          <t>2,11; 8,34</t>
         </is>
       </c>
       <c r="F37" s="2" t="inlineStr">
         <is>
-          <t>-16,79; -7,81</t>
+          <t>8,25; 16,95</t>
         </is>
       </c>
       <c r="G37" s="2" t="inlineStr">
         <is>
-          <t>-12,24; -3,82</t>
+          <t>4,06; 12,52</t>
         </is>
       </c>
       <c r="H37" s="2" t="inlineStr">
         <is>
-          <t>-10,72; 4,74</t>
+          <t>-4,5; 10,56</t>
         </is>
       </c>
       <c r="I37" s="2" t="inlineStr">
         <is>
-          <t>-12,97; -7,18</t>
+          <t>7,18; 12,99</t>
         </is>
       </c>
       <c r="J37" s="2" t="inlineStr">
         <is>
-          <t>-9,17; -3,35</t>
+          <t>3,66; 9,1</t>
         </is>
       </c>
       <c r="K37" s="2" t="inlineStr">
         <is>
-          <t>-8,37; 0,46</t>
+          <t>-1,59; 8,36</t>
         </is>
       </c>
     </row>
@@ -2458,47 +2458,47 @@
       </c>
       <c r="C38" s="2" t="inlineStr">
         <is>
-          <t>-7,59%</t>
+          <t>87,97%</t>
         </is>
       </c>
       <c r="D38" s="2" t="inlineStr">
         <is>
-          <t>-4,25%</t>
+          <t>49,28%</t>
         </is>
       </c>
       <c r="E38" s="2" t="inlineStr">
         <is>
-          <t>-5,63%</t>
+          <t>65,32%</t>
         </is>
       </c>
       <c r="F38" s="2" t="inlineStr">
         <is>
-          <t>-14,38%</t>
+          <t>92,46%</t>
         </is>
       </c>
       <c r="G38" s="2" t="inlineStr">
         <is>
-          <t>-9,51%</t>
+          <t>61,17%</t>
         </is>
       </c>
       <c r="H38" s="2" t="inlineStr">
         <is>
-          <t>-5,59%</t>
+          <t>35,94%</t>
         </is>
       </c>
       <c r="I38" s="2" t="inlineStr">
         <is>
-          <t>-11,34%</t>
+          <t>90,74%</t>
         </is>
       </c>
       <c r="J38" s="2" t="inlineStr">
         <is>
-          <t>-7,13%</t>
+          <t>57,04%</t>
         </is>
       </c>
       <c r="K38" s="2" t="inlineStr">
         <is>
-          <t>-5,84%</t>
+          <t>46,72%</t>
         </is>
       </c>
     </row>
@@ -2511,47 +2511,47 @@
       </c>
       <c r="C39" s="2" t="inlineStr">
         <is>
-          <t>-11,75; -3,35</t>
+          <t>30,18; 167,72</t>
         </is>
       </c>
       <c r="D39" s="2" t="inlineStr">
         <is>
-          <t>-7,78; -0,36</t>
+          <t>2,59; 107,08</t>
         </is>
       </c>
       <c r="E39" s="2" t="inlineStr">
         <is>
-          <t>-8,89; -2,22</t>
+          <t>18,31; 127,91</t>
         </is>
       </c>
       <c r="F39" s="2" t="inlineStr">
         <is>
-          <t>-19,08; -9,59</t>
+          <t>53,01; 148,31</t>
         </is>
       </c>
       <c r="G39" s="2" t="inlineStr">
         <is>
-          <t>-13,84; -4,53</t>
+          <t>24,72; 107,54</t>
         </is>
       </c>
       <c r="H39" s="2" t="inlineStr">
         <is>
-          <t>-12,29; 5,53</t>
+          <t>-28,38; 85,25</t>
         </is>
       </c>
       <c r="I39" s="2" t="inlineStr">
         <is>
-          <t>-14,43; -8,1</t>
+          <t>57,68; 133,08</t>
         </is>
       </c>
       <c r="J39" s="2" t="inlineStr">
         <is>
-          <t>-10,31; -3,86</t>
+          <t>30,0; 94,43</t>
         </is>
       </c>
       <c r="K39" s="2" t="inlineStr">
         <is>
-          <t>-9,32; 0,81</t>
+          <t>-7,17; 83,15</t>
         </is>
       </c>
     </row>

--- a/data/trans_camb/BARTHEL_R2-Provincia-trans_camb.xlsx
+++ b/data/trans_camb/BARTHEL_R2-Provincia-trans_camb.xlsx
@@ -523,7 +523,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población con dependencia funcional, al menos moderada, para actividades básicas de la vida diaria (Barthel)</t>
+          <t>Población con dependencia funcional para actividades básicas de la vida diaria de grado moderado o superior (Barthel)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -634,7 +634,7 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>-4,1</t>
+          <t>-4,73</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
@@ -649,7 +649,7 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>7,05</t>
+          <t>6,92</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
@@ -664,7 +664,7 @@
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>1,81</t>
+          <t>1,33</t>
         </is>
       </c>
     </row>
@@ -677,47 +677,47 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-8,77; 20,57</t>
+          <t>-8,79; 20,36</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-0,31; 32,05</t>
+          <t>1,41; 32,07</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-16,44; 5,62</t>
+          <t>-18,68; 4,0</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>22,45; 54,52</t>
+          <t>21,73; 55,89</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>14,39; 47,99</t>
+          <t>12,98; 46,77</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>-5,98; 16,11</t>
+          <t>-7,45; 14,98</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>11,3; 34,19</t>
+          <t>11,62; 35,21</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>12,77; 37,33</t>
+          <t>12,42; 36,71</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>-6,7; 9,08</t>
+          <t>-7,38; 7,9</t>
         </is>
       </c>
     </row>
@@ -740,7 +740,7 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>-41,18%</t>
+          <t>-47,54%</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
@@ -755,7 +755,7 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>115,31%</t>
+          <t>113,07%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
@@ -770,7 +770,7 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>22,78%</t>
+          <t>16,72%</t>
         </is>
       </c>
     </row>
@@ -783,47 +783,47 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-63,81; 597,84</t>
+          <t>-60,39; 570,12</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-16,31; 738,07</t>
+          <t>1,07; 1018,64</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-88,83; 289,62</t>
+          <t>-92,12; 186,95</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>98,75; —</t>
+          <t>100,16; —</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>31,31; —</t>
+          <t>48,09; —</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>-50,96; —</t>
+          <t>-53,47; —</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>70,19; 1067,22</t>
+          <t>78,35; 930,48</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>88,62; 995,87</t>
+          <t>82,63; 1063,44</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>-51,93; 299,96</t>
+          <t>-52,62; 231,85</t>
         </is>
       </c>
     </row>
@@ -850,7 +850,7 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>7,39</t>
+          <t>7,15</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
@@ -865,7 +865,7 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>13,62</t>
+          <t>14,22</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
@@ -880,7 +880,7 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>11,39</t>
+          <t>11,51</t>
         </is>
       </c>
     </row>
@@ -893,47 +893,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>1,87; 23,53</t>
+          <t>0,96; 23,49</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-5,75; 8,5</t>
+          <t>-5,88; 8,48</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-0,42; 15,33</t>
+          <t>-1,36; 15,11</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>8,69; 32,01</t>
+          <t>8,26; 31,97</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-2,55; 20,39</t>
+          <t>-3,18; 20,04</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>4,38; 22,19</t>
+          <t>5,08; 23,47</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>7,94; 24,72</t>
+          <t>8,34; 24,58</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>-2,13; 12,89</t>
+          <t>-1,78; 12,48</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>4,92; 18,01</t>
+          <t>4,21; 17,56</t>
         </is>
       </c>
     </row>
@@ -956,7 +956,7 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>164,22%</t>
+          <t>158,92%</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
@@ -971,7 +971,7 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>98,14%</t>
+          <t>102,48%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
@@ -986,7 +986,7 @@
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>113,05%</t>
+          <t>114,16%</t>
         </is>
       </c>
     </row>
@@ -999,47 +999,47 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-29,43; 1652,66</t>
+          <t>-21,07; 1269,78</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-77,47; 653,82</t>
+          <t>-75,74; 551,24</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-28,87; 1239,95</t>
+          <t>-31,93; 1072,83</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>44,28; 351,58</t>
+          <t>34,92; 353,41</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-18,16; 229,58</t>
+          <t>-19,05; 229,91</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>17,75; 262,06</t>
+          <t>21,68; 258,42</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>53,04; 384,9</t>
+          <t>54,81; 384,51</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>-19,02; 199,5</t>
+          <t>-16,94; 185,89</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>33,16; 272,66</t>
+          <t>27,93; 267,64</t>
         </is>
       </c>
     </row>
@@ -1066,7 +1066,7 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>19,24</t>
+          <t>18,98</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
@@ -1081,7 +1081,7 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>13,02</t>
+          <t>13,74</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
@@ -1096,7 +1096,7 @@
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>15,27</t>
+          <t>15,53</t>
         </is>
       </c>
     </row>
@@ -1109,47 +1109,47 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-0,38; 24,87</t>
+          <t>0,0; 25,48</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-7,25; 10,93</t>
+          <t>-7,83; 10,34</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>8,48; 29,64</t>
+          <t>8,66; 27,52</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-3,3; 22,45</t>
+          <t>-2,21; 21,5</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-13,72; 8,17</t>
+          <t>-14,15; 7,81</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>2,57; 23,31</t>
+          <t>2,55; 22,75</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>1,24; 18,79</t>
+          <t>1,09; 18,71</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>-8,4; 6,54</t>
+          <t>-8,92; 5,56</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>7,89; 22,5</t>
+          <t>7,41; 22,4</t>
         </is>
       </c>
     </row>
@@ -1172,7 +1172,7 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>334,18%</t>
+          <t>329,5%</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
@@ -1187,7 +1187,7 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>98,04%</t>
+          <t>103,43%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
@@ -1202,7 +1202,7 @@
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>146,38%</t>
+          <t>148,88%</t>
         </is>
       </c>
     </row>
@@ -1215,47 +1215,47 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>-33,13; 1489,81</t>
+          <t>-25,71; —</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>-77,73; —</t>
+          <t>-73,98; —</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>42,42; 1485,87</t>
+          <t>59,14; 1484,1</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>-19,0; 275,37</t>
+          <t>-16,33; 270,62</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>-77,0; 123,93</t>
+          <t>-77,85; 107,24</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>11,73; 318,6</t>
+          <t>11,47; 304,17</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>6,52; 297,94</t>
+          <t>3,09; 289,49</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>-61,87; 96,33</t>
+          <t>-61,01; 88,01</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>48,07; 375,55</t>
+          <t>45,28; 358,47</t>
         </is>
       </c>
     </row>
@@ -1282,7 +1282,7 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>4,68</t>
+          <t>3,91</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
@@ -1297,7 +1297,7 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>4,47</t>
+          <t>4,1</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
@@ -1312,7 +1312,7 @@
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>4,64</t>
+          <t>3,98</t>
         </is>
       </c>
     </row>
@@ -1325,47 +1325,47 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>-0,28; 19,89</t>
+          <t>-1,39; 19,42</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>3,06; 23,23</t>
+          <t>2,94; 23,64</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>-3,47; 11,49</t>
+          <t>-3,5; 10,21</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>-4,32; 20,15</t>
+          <t>-4,82; 20,56</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>-5,96; 20,67</t>
+          <t>-5,55; 19,38</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>-5,45; 13,75</t>
+          <t>-6,14; 12,47</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>-0,11; 17,06</t>
+          <t>-0,62; 16,54</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>0,81; 18,43</t>
+          <t>0,41; 17,91</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>-2,12; 10,55</t>
+          <t>-3,05; 10,04</t>
         </is>
       </c>
     </row>
@@ -1388,7 +1388,7 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>100,07%</t>
+          <t>83,48%</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
@@ -1403,7 +1403,7 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>28,46%</t>
+          <t>26,14%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
@@ -1418,7 +1418,7 @@
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>42,13%</t>
+          <t>36,17%</t>
         </is>
       </c>
     </row>
@@ -1431,47 +1431,47 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>-28,45; 1216,81</t>
+          <t>-41,05; 1582,62</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>4,43; 1328,51</t>
+          <t>7,41; 1456,14</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>-51,0; 632,63</t>
+          <t>-49,37; 639,71</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>-24,1; 220,76</t>
+          <t>-26,16; 217,07</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>-32,25; 204,71</t>
+          <t>-29,54; 196,36</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>-25,82; 152,53</t>
+          <t>-28,32; 132,49</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>-3,96; 241,6</t>
+          <t>-5,7; 235,0</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>3,08; 256,01</t>
+          <t>-0,18; 250,17</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>-13,64; 157,67</t>
+          <t>-19,93; 152,91</t>
         </is>
       </c>
     </row>
@@ -1498,7 +1498,7 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>-0,05</t>
+          <t>-0,44</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
@@ -1513,7 +1513,7 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>1,96</t>
+          <t>2,14</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
@@ -1528,7 +1528,7 @@
       </c>
       <c r="K20" s="2" t="inlineStr">
         <is>
-          <t>1,38</t>
+          <t>1,34</t>
         </is>
       </c>
     </row>
@@ -1541,47 +1541,47 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>-14,99; 24,33</t>
+          <t>-14,44; 25,2</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>-28,81; -1,83</t>
+          <t>-29,94; -1,64</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>-16,09; 13,35</t>
+          <t>-18,13; 13,28</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>-9,92; 25,82</t>
+          <t>-10,37; 24,52</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>-15,31; 16,57</t>
+          <t>-17,16; 17,98</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>-13,39; 14,21</t>
+          <t>-14,62; 15,24</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>-7,64; 19,86</t>
+          <t>-5,85; 20,1</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>-17,6; 6,37</t>
+          <t>-18,3; 4,87</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>-9,27; 11,22</t>
+          <t>-9,28; 11,58</t>
         </is>
       </c>
     </row>
@@ -1604,7 +1604,7 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>-0,3%</t>
+          <t>-2,49%</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
@@ -1619,7 +1619,7 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>9,32%</t>
+          <t>10,18%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
@@ -1634,7 +1634,7 @@
       </c>
       <c r="K22" s="2" t="inlineStr">
         <is>
-          <t>7,04%</t>
+          <t>6,82%</t>
         </is>
       </c>
     </row>
@@ -1647,47 +1647,47 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>-63,66; 288,05</t>
+          <t>-63,94; 303,17</t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>-100,0; 31,72</t>
+          <t>-100,0; 40,21</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>-61,41; 154,78</t>
+          <t>-61,88; 175,92</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>-35,36; 209,11</t>
+          <t>-37,33; 214,15</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>-52,26; 143,68</t>
+          <t>-61,74; 169,6</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>-42,24; 127,07</t>
+          <t>-44,8; 153,79</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>-30,38; 159,39</t>
+          <t>-27,13; 165,7</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
         <is>
-          <t>-65,26; 58,44</t>
+          <t>-67,94; 46,75</t>
         </is>
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>-34,54; 95,08</t>
+          <t>-33,67; 101,76</t>
         </is>
       </c>
     </row>
@@ -1714,7 +1714,7 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>14,77</t>
+          <t>14,84</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
@@ -1729,7 +1729,7 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>19,15</t>
+          <t>19,31</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
@@ -1744,7 +1744,7 @@
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>16,59</t>
+          <t>16,79</t>
         </is>
       </c>
     </row>
@@ -1757,47 +1757,47 @@
       </c>
       <c r="C25" s="2" t="inlineStr">
         <is>
-          <t>2,47; 29,12</t>
+          <t>0,94; 28,96</t>
         </is>
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t>1,68; 27,75</t>
+          <t>0,1; 25,54</t>
         </is>
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>4,07; 24,09</t>
+          <t>1,8; 23,76</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>-0,1; 27,32</t>
+          <t>-0,06; 27,94</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
         <is>
-          <t>5,09; 35,56</t>
+          <t>3,76; 34,6</t>
         </is>
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>6,31; 28,77</t>
+          <t>7,62; 29,33</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>4,7; 22,52</t>
+          <t>4,55; 23,9</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
         <is>
-          <t>6,11; 27,17</t>
+          <t>5,45; 26,65</t>
         </is>
       </c>
       <c r="K25" s="2" t="inlineStr">
         <is>
-          <t>8,51; 24,36</t>
+          <t>8,47; 23,97</t>
         </is>
       </c>
     </row>
@@ -1820,7 +1820,7 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>189,08%</t>
+          <t>189,97%</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
@@ -1835,7 +1835,7 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>140,71%</t>
+          <t>141,95%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
@@ -1850,7 +1850,7 @@
       </c>
       <c r="K26" s="2" t="inlineStr">
         <is>
-          <t>147,1%</t>
+          <t>148,88%</t>
         </is>
       </c>
     </row>
@@ -1863,47 +1863,47 @@
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>-9,79; 1188,72</t>
+          <t>-12,01; 1050,21</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>-5,22; 1061,11</t>
+          <t>-13,67; 863,35</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>13,33; 1116,85</t>
+          <t>3,49; 1015,36</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>-6,7; 345,25</t>
+          <t>-3,66; 412,75</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
         <is>
-          <t>10,76; 428,83</t>
+          <t>15,28; 519,8</t>
         </is>
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>29,78; 458,44</t>
+          <t>28,78; 387,17</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>24,01; 339,46</t>
+          <t>22,51; 338,31</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
         <is>
-          <t>34,71; 407,14</t>
+          <t>31,11; 363,73</t>
         </is>
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>43,48; 403,07</t>
+          <t>48,76; 361,16</t>
         </is>
       </c>
     </row>
@@ -1930,7 +1930,7 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>7,71</t>
+          <t>7,32</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
@@ -1945,7 +1945,7 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>5,42</t>
+          <t>20,12</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
@@ -1960,7 +1960,7 @@
       </c>
       <c r="K28" s="2" t="inlineStr">
         <is>
-          <t>6,03</t>
+          <t>13,97</t>
         </is>
       </c>
     </row>
@@ -1973,47 +1973,47 @@
       </c>
       <c r="C29" s="2" t="inlineStr">
         <is>
-          <t>2,99; 19,34</t>
+          <t>3,83; 20,33</t>
         </is>
       </c>
       <c r="D29" s="2" t="inlineStr">
         <is>
-          <t>1,88; 17,16</t>
+          <t>2,32; 16,81</t>
         </is>
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>1,49; 13,92</t>
+          <t>1,38; 13,54</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>9,83; 25,59</t>
+          <t>10,03; 26,02</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
         <is>
-          <t>14,42; 31,58</t>
+          <t>13,91; 31,25</t>
         </is>
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>-5,29; 22,69</t>
+          <t>13,5; 26,47</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>9,23; 20,86</t>
+          <t>8,81; 20,52</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
         <is>
-          <t>11,72; 23,21</t>
+          <t>10,81; 22,81</t>
         </is>
       </c>
       <c r="K29" s="2" t="inlineStr">
         <is>
-          <t>-3,49; 15,36</t>
+          <t>9,51; 18,51</t>
         </is>
       </c>
     </row>
@@ -2036,7 +2036,7 @@
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>187,09%</t>
+          <t>177,54%</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
@@ -2051,7 +2051,7 @@
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>130,83%</t>
+          <t>485,93%</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
@@ -2066,7 +2066,7 @@
       </c>
       <c r="K30" s="2" t="inlineStr">
         <is>
-          <t>146,01%</t>
+          <t>338,24%</t>
         </is>
       </c>
     </row>
@@ -2079,47 +2079,47 @@
       </c>
       <c r="C31" s="2" t="inlineStr">
         <is>
-          <t>17,7; 1106,13</t>
+          <t>31,16; 1034,92</t>
         </is>
       </c>
       <c r="D31" s="2" t="inlineStr">
         <is>
-          <t>-0,64; 942,18</t>
+          <t>15,87; 892,49</t>
         </is>
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>9,68; 763,12</t>
+          <t>10,98; 804,61</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>117,1; 1449,72</t>
+          <t>121,04; 1250,54</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
         <is>
-          <t>168,74; 2130,65</t>
+          <t>173,24; 1717,29</t>
         </is>
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>-66,02; 786,93</t>
+          <t>171,2; 1418,5</t>
         </is>
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>121,79; 811,2</t>
+          <t>131,76; 838,89</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr">
         <is>
-          <t>159,5; 937,9</t>
+          <t>159,37; 950,17</t>
         </is>
       </c>
       <c r="K31" s="2" t="inlineStr">
         <is>
-          <t>-37,51; 467,52</t>
+          <t>134,98; 762,48</t>
         </is>
       </c>
     </row>
@@ -2146,7 +2146,7 @@
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>-4,39</t>
+          <t>-3,98</t>
         </is>
       </c>
       <c r="F32" s="2" t="inlineStr">
@@ -2161,7 +2161,7 @@
       </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
-          <t>-0,82</t>
+          <t>-0,26</t>
         </is>
       </c>
       <c r="I32" s="2" t="inlineStr">
@@ -2176,7 +2176,7 @@
       </c>
       <c r="K32" s="2" t="inlineStr">
         <is>
-          <t>-2,51</t>
+          <t>-1,95</t>
         </is>
       </c>
     </row>
@@ -2189,47 +2189,47 @@
       </c>
       <c r="C33" s="2" t="inlineStr">
         <is>
-          <t>-12,67; 4,2</t>
+          <t>-12,1; 4,28</t>
         </is>
       </c>
       <c r="D33" s="2" t="inlineStr">
         <is>
-          <t>-11,9; 3,74</t>
+          <t>-12,86; 3,63</t>
         </is>
       </c>
       <c r="E33" s="2" t="inlineStr">
         <is>
-          <t>-12,03; 2,64</t>
+          <t>-11,78; 2,85</t>
         </is>
       </c>
       <c r="F33" s="2" t="inlineStr">
         <is>
-          <t>-8,72; 9,42</t>
+          <t>-9,35; 9,28</t>
         </is>
       </c>
       <c r="G33" s="2" t="inlineStr">
         <is>
-          <t>-14,17; 3,74</t>
+          <t>-14,52; 3,21</t>
         </is>
       </c>
       <c r="H33" s="2" t="inlineStr">
         <is>
-          <t>-9,19; 6,79</t>
+          <t>-8,35; 8,01</t>
         </is>
       </c>
       <c r="I33" s="2" t="inlineStr">
         <is>
-          <t>-7,88; 5,52</t>
+          <t>-7,7; 4,91</t>
         </is>
       </c>
       <c r="J33" s="2" t="inlineStr">
         <is>
-          <t>-10,73; 1,28</t>
+          <t>-10,92; 1,27</t>
         </is>
       </c>
       <c r="K33" s="2" t="inlineStr">
         <is>
-          <t>-7,98; 2,95</t>
+          <t>-7,81; 3,95</t>
         </is>
       </c>
     </row>
@@ -2252,7 +2252,7 @@
       </c>
       <c r="E34" s="2" t="inlineStr">
         <is>
-          <t>-33,48%</t>
+          <t>-30,36%</t>
         </is>
       </c>
       <c r="F34" s="2" t="inlineStr">
@@ -2267,7 +2267,7 @@
       </c>
       <c r="H34" s="2" t="inlineStr">
         <is>
-          <t>-4,29%</t>
+          <t>-1,34%</t>
         </is>
       </c>
       <c r="I34" s="2" t="inlineStr">
@@ -2282,7 +2282,7 @@
       </c>
       <c r="K34" s="2" t="inlineStr">
         <is>
-          <t>-15,13%</t>
+          <t>-11,79%</t>
         </is>
       </c>
     </row>
@@ -2295,47 +2295,47 @@
       </c>
       <c r="C35" s="2" t="inlineStr">
         <is>
-          <t>-72,28; 57,16</t>
+          <t>-71,52; 51,26</t>
         </is>
       </c>
       <c r="D35" s="2" t="inlineStr">
         <is>
-          <t>-67,22; 49,7</t>
+          <t>-69,9; 48,99</t>
         </is>
       </c>
       <c r="E35" s="2" t="inlineStr">
         <is>
-          <t>-64,66; 36,86</t>
+          <t>-62,85; 34,49</t>
         </is>
       </c>
       <c r="F35" s="2" t="inlineStr">
         <is>
-          <t>-37,98; 69,05</t>
+          <t>-39,74; 66,87</t>
         </is>
       </c>
       <c r="G35" s="2" t="inlineStr">
         <is>
-          <t>-61,61; 27,24</t>
+          <t>-61,21; 22,7</t>
         </is>
       </c>
       <c r="H35" s="2" t="inlineStr">
         <is>
-          <t>-37,08; 51,72</t>
+          <t>-33,93; 60,0</t>
         </is>
       </c>
       <c r="I35" s="2" t="inlineStr">
         <is>
-          <t>-39,3; 44,22</t>
+          <t>-39,4; 40,3</t>
         </is>
       </c>
       <c r="J35" s="2" t="inlineStr">
         <is>
-          <t>-56,61; 7,74</t>
+          <t>-56,08; 10,74</t>
         </is>
       </c>
       <c r="K35" s="2" t="inlineStr">
         <is>
-          <t>-39,12; 23,05</t>
+          <t>-36,32; 34,75</t>
         </is>
       </c>
     </row>
@@ -2362,7 +2362,7 @@
       </c>
       <c r="E36" s="2" t="inlineStr">
         <is>
-          <t>5,19</t>
+          <t>4,71</t>
         </is>
       </c>
       <c r="F36" s="2" t="inlineStr">
@@ -2377,7 +2377,7 @@
       </c>
       <c r="H36" s="2" t="inlineStr">
         <is>
-          <t>4,84</t>
+          <t>9,57</t>
         </is>
       </c>
       <c r="I36" s="2" t="inlineStr">
@@ -2392,7 +2392,7 @@
       </c>
       <c r="K36" s="2" t="inlineStr">
         <is>
-          <t>5,19</t>
+          <t>7,32</t>
         </is>
       </c>
     </row>
@@ -2405,47 +2405,47 @@
       </c>
       <c r="C37" s="2" t="inlineStr">
         <is>
-          <t>2,99; 10,37</t>
+          <t>3,09; 10,84</t>
         </is>
       </c>
       <c r="D37" s="2" t="inlineStr">
         <is>
-          <t>0,31; 7,05</t>
+          <t>0,53; 7,27</t>
         </is>
       </c>
       <c r="E37" s="2" t="inlineStr">
         <is>
-          <t>2,11; 8,34</t>
+          <t>1,52; 7,6</t>
         </is>
       </c>
       <c r="F37" s="2" t="inlineStr">
         <is>
-          <t>8,25; 16,95</t>
+          <t>8,12; 16,97</t>
         </is>
       </c>
       <c r="G37" s="2" t="inlineStr">
         <is>
-          <t>4,06; 12,52</t>
+          <t>3,89; 12,69</t>
         </is>
       </c>
       <c r="H37" s="2" t="inlineStr">
         <is>
-          <t>-4,5; 10,56</t>
+          <t>6,37; 13,13</t>
         </is>
       </c>
       <c r="I37" s="2" t="inlineStr">
         <is>
-          <t>7,18; 12,99</t>
+          <t>7,09; 13,03</t>
         </is>
       </c>
       <c r="J37" s="2" t="inlineStr">
         <is>
-          <t>3,66; 9,1</t>
+          <t>3,59; 9,18</t>
         </is>
       </c>
       <c r="K37" s="2" t="inlineStr">
         <is>
-          <t>-1,59; 8,36</t>
+          <t>4,71; 9,86</t>
         </is>
       </c>
     </row>
@@ -2468,7 +2468,7 @@
       </c>
       <c r="E38" s="2" t="inlineStr">
         <is>
-          <t>65,32%</t>
+          <t>59,32%</t>
         </is>
       </c>
       <c r="F38" s="2" t="inlineStr">
@@ -2483,7 +2483,7 @@
       </c>
       <c r="H38" s="2" t="inlineStr">
         <is>
-          <t>35,94%</t>
+          <t>71,09%</t>
         </is>
       </c>
       <c r="I38" s="2" t="inlineStr">
@@ -2498,7 +2498,7 @@
       </c>
       <c r="K38" s="2" t="inlineStr">
         <is>
-          <t>46,72%</t>
+          <t>65,9%</t>
         </is>
       </c>
     </row>
@@ -2511,47 +2511,47 @@
       </c>
       <c r="C39" s="2" t="inlineStr">
         <is>
-          <t>30,18; 167,72</t>
+          <t>30,64; 168,44</t>
         </is>
       </c>
       <c r="D39" s="2" t="inlineStr">
         <is>
-          <t>2,59; 107,08</t>
+          <t>5,34; 115,88</t>
         </is>
       </c>
       <c r="E39" s="2" t="inlineStr">
         <is>
-          <t>18,31; 127,91</t>
+          <t>14,8; 125,93</t>
         </is>
       </c>
       <c r="F39" s="2" t="inlineStr">
         <is>
-          <t>53,01; 148,31</t>
+          <t>50,61; 147,56</t>
         </is>
       </c>
       <c r="G39" s="2" t="inlineStr">
         <is>
-          <t>24,72; 107,54</t>
+          <t>24,13; 110,88</t>
         </is>
       </c>
       <c r="H39" s="2" t="inlineStr">
         <is>
-          <t>-28,38; 85,25</t>
+          <t>41,06; 118,02</t>
         </is>
       </c>
       <c r="I39" s="2" t="inlineStr">
         <is>
-          <t>57,68; 133,08</t>
+          <t>56,37; 133,21</t>
         </is>
       </c>
       <c r="J39" s="2" t="inlineStr">
         <is>
-          <t>30,0; 94,43</t>
+          <t>29,49; 93,4</t>
         </is>
       </c>
       <c r="K39" s="2" t="inlineStr">
         <is>
-          <t>-7,17; 83,15</t>
+          <t>35,19; 101,31</t>
         </is>
       </c>
     </row>
